--- a/src/Excelsior.Tests/NullableTests.NullDisplay.verified.xlsx
+++ b/src/Excelsior.Tests/NullableTests.NullDisplay.verified.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
   </sheets>
 </workbook>
 </file>
@@ -42,15 +42,15 @@
     </border>
   </borders>
   <cellXfs count="5">
-    <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
-    <xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
-    <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -58,12 +58,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
@@ -155,7 +155,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="b">
-        <v>true</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/src/Excelsior.Tests/NullableTests.NullDisplay.verified.xlsx
+++ b/src/Excelsior.Tests/NullableTests.NullDisplay.verified.xlsx
@@ -160,5 +160,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F3"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E3">
+      <formula1>"Value"</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>
--- a/src/Excelsior.Tests/NullableTests.NullDisplay.verified.xlsx
+++ b/src/Excelsior.Tests/NullableTests.NullDisplay.verified.xlsx
@@ -160,9 +160,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F3"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="E2:E3">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E3">
       <formula1>"Value"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F3">
+      <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
 </worksheet>

--- a/src/Excelsior.Tests/NullableTests.NullDisplay.verified.xlsx
+++ b/src/Excelsior.Tests/NullableTests.NullDisplay.verified.xlsx
@@ -161,10 +161,10 @@
   </sheetData>
   <autoFilter ref="A1:F3"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Value." sqref="E2:E3">
       <formula1>"Value"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="F2:F3">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/NullableTests.NullDisplay.verified.xlsx
+++ b/src/Excelsior.Tests/NullableTests.NullDisplay.verified.xlsx
@@ -54,6 +54,15 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -160,11 +169,53 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F3"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Value." sqref="E2:E3">
+  <conditionalFormatting sqref="A2:A3">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(A2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B3">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(B2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C3">
+    <cfRule type="containsBlanks" dxfId="0" priority="3">
+      <formula>LEN(TRIM(C2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D3">
+    <cfRule type="containsBlanks" dxfId="0" priority="4">
+      <formula>LEN(TRIM(D2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E3">
+    <cfRule type="containsBlanks" dxfId="0" priority="5">
+      <formula>LEN(TRIM(E2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F3">
+    <cfRule type="containsBlanks" dxfId="0" priority="6">
+      <formula>LEN(TRIM(F2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="6">
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="A2:A3">
+      <formula1>LEN(TRIM(A2))&gt;0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="B2:B3">
+      <formula1>LEN(TRIM(B2))&gt;0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="C2:C3">
+      <formula1>LEN(TRIM(C2))&gt;0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="D2:D3">
+      <formula1>LEN(TRIM(D2))&gt;0</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Value." sqref="E2:E3">
       <formula1>"Value"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="F2:F3">
+    <dataValidation type="list" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="F2:F3">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/NullableTests.NullDisplay.verified.xlsx
+++ b/src/Excelsior.Tests/NullableTests.NullDisplay.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -220,4 +220,17 @@
     </dataValidation>
   </dataValidations>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Sheet1">
+    <column index="1" property="Number"/>
+    <column index="2" property="String"/>
+    <column index="3" property="DateTime"/>
+    <column index="4" property="Date"/>
+    <column index="5" property="Enum"/>
+    <column index="6" property="Bool"/>
+  </sheet>
+</columnMetadata>
 </file>
--- a/src/Excelsior.Tests/NullableTests.NullDisplay.verified.xlsx
+++ b/src/Excelsior.Tests/NullableTests.NullDisplay.verified.xlsx
@@ -167,55 +167,81 @@
         <v>true</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other</t>
+        </is>
+      </c>
+      <c r="C4" s="3">
+        <v>44229.469513888886</v>
+      </c>
+      <c r="D4" s="4">
+        <v>44229</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="b">
+        <v>false</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F3"/>
-  <conditionalFormatting sqref="A2:A3">
+  <autoFilter ref="A1:F4"/>
+  <conditionalFormatting sqref="A2:A4">
     <cfRule type="containsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B3">
+  <conditionalFormatting sqref="B2:B4">
     <cfRule type="containsBlanks" dxfId="0" priority="2">
       <formula>LEN(TRIM(B2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C3">
+  <conditionalFormatting sqref="C2:C4">
     <cfRule type="containsBlanks" dxfId="0" priority="3">
       <formula>LEN(TRIM(C2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D3">
+  <conditionalFormatting sqref="D2:D4">
     <cfRule type="containsBlanks" dxfId="0" priority="4">
       <formula>LEN(TRIM(D2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E3">
+  <conditionalFormatting sqref="E2:E4">
     <cfRule type="containsBlanks" dxfId="0" priority="5">
       <formula>LEN(TRIM(E2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F3">
+  <conditionalFormatting sqref="F2:F4">
     <cfRule type="containsBlanks" dxfId="0" priority="6">
       <formula>LEN(TRIM(F2))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="A2:A3">
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="A2:A4">
       <formula1>LEN(TRIM(A2))&gt;0</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="B2:B3">
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="B2:B4">
       <formula1>LEN(TRIM(B2))&gt;0</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="C2:C3">
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="C2:C4">
       <formula1>LEN(TRIM(C2))&gt;0</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="D2:D3">
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="D2:D4">
       <formula1>LEN(TRIM(D2))&gt;0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Value." sqref="E2:E3">
+    <dataValidation type="list" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Value." sqref="E2:E4">
       <formula1>"Value"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="F2:F3">
+    <dataValidation type="list" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="F2:F4">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/NullableTests.NullDisplay.verified.xlsx
+++ b/src/Excelsior.Tests/NullableTests.NullDisplay.verified.xlsx
@@ -164,7 +164,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="b">
-        <v>true</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -190,7 +190,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="b">
-        <v>false</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/src/Excelsior.Tests/NullableTests.NullDisplay.verified.xlsx
+++ b/src/Excelsior.Tests/NullableTests.NullDisplay.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -54,6 +54,15 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -155,10 +164,99 @@
         </is>
       </c>
       <c r="F3" s="2" t="b">
-        <v>true</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other</t>
+        </is>
+      </c>
+      <c r="C4" s="3">
+        <v>44229.469513888886</v>
+      </c>
+      <c r="D4" s="4">
+        <v>44229</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F3"/>
+  <autoFilter ref="A1:F4"/>
+  <conditionalFormatting sqref="A2:A4">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(A2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B4">
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(B2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C4">
+    <cfRule type="containsBlanks" dxfId="0" priority="3">
+      <formula>LEN(TRIM(C2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D4">
+    <cfRule type="containsBlanks" dxfId="0" priority="4">
+      <formula>LEN(TRIM(D2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E4">
+    <cfRule type="containsBlanks" dxfId="0" priority="5">
+      <formula>LEN(TRIM(E2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F4">
+    <cfRule type="containsBlanks" dxfId="0" priority="6">
+      <formula>LEN(TRIM(F2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="6">
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="A2:A4">
+      <formula1>LEN(TRIM(A2))&gt;0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="B2:B4">
+      <formula1>LEN(TRIM(B2))&gt;0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="C2:C4">
+      <formula1>LEN(TRIM(C2))&gt;0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="D2:D4">
+      <formula1>LEN(TRIM(D2))&gt;0</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Value." sqref="E2:E4">
+      <formula1>"Value"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="F2:F4">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Sheet1">
+    <column index="1" property="Number"/>
+    <column index="2" property="String"/>
+    <column index="3" property="DateTime"/>
+    <column index="4" property="Date"/>
+    <column index="5" property="Enum"/>
+    <column index="6" property="Bool"/>
+  </sheet>
+</columnMetadata>
 </file>
--- a/src/Excelsior.Tests/NullableTests.NullDisplay.verified.xlsx
+++ b/src/Excelsior.Tests/NullableTests.NullDisplay.verified.xlsx
@@ -71,8 +71,8 @@
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
